--- a/SuppXLS/Scen_z_MACC-TRA.xlsx
+++ b/SuppXLS/Scen_z_MACC-TRA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4C89D0-C068-47D7-BF74-6A186BEB1D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D130297-A9BC-421B-9034-1D955EE052D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,9 +223,6 @@
     <t>T-LGT-FCV_HYD61, T-MGT-FCV_HYD71, T-HGT-FCV_HYD81</t>
   </si>
   <si>
-    <t>2025-2050</t>
-  </si>
-  <si>
     <t>FT-TRAGSL</t>
   </si>
   <si>
@@ -242,6 +239,9 @@
   </si>
   <si>
     <t>TRABDL</t>
+  </si>
+  <si>
+    <t>2026-2050</t>
   </si>
 </sst>
 </file>
@@ -781,7 +781,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -809,7 +809,7 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -823,7 +823,7 @@
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -837,7 +837,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -851,7 +851,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -893,7 +893,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -964,10 +964,10 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
         <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>33</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -976,18 +976,18 @@
         <v>5</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>32</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -996,18 +996,18 @@
         <v>5</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
       </c>
       <c r="E22">
         <v>2030</v>
@@ -1016,18 +1016,18 @@
         <v>0.1</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
         <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
       </c>
       <c r="E23">
         <v>2030</v>
@@ -1036,10 +1036,10 @@
         <v>0.2</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
